--- a/pensum/ok08/LOM_Ovingsark_Okonomistyring_kap08_Nullpunkt_NY.xlsx
+++ b/pensum/ok08/LOM_Ovingsark_Okonomistyring_kap08_Nullpunkt_NY.xlsx
@@ -319,7 +319,7 @@
     <t xml:space="preserve">Bransjetall: NHO Elektro, Lønnsomhetsrapport 2025, gjengitt i Elektro 24-7 19.08.2026 (hentet 10.09.2026). De 809 er bedriftene i datagrunnlaget, ikke bransjen. NHO Elektro oppgir ikke svarprosent.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nordlys Elektro AS er en konstruert casebedrift. Tallene henger sammen på tvers av alle ti kapitlene i Bok 1.</t>
+    <t xml:space="preserve">Nordlys Elektro AS er en konstruert casebedrift. Tallene henger sammen på tvers av alle ti kapitlene i Økonomistyring for LØM-emnet.</t>
   </si>
   <si>
     <t xml:space="preserve">Hvor mange oppdrag må til før avdelingen tjener penger?</t>
@@ -472,7 +472,7 @@
     <t xml:space="preserve">Prøv dette: sett planlagt antall i B21 opp til dommen i D30 snur. Det tallet er nullpunktet, og det er hele kapitlet.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Bok 1 kap. 8.1 og 8.2, og formlene for nullpunkt og risikomargin i formelsamlingen. Tallene er serviceavdelingen i Nordlys Elektro AS.</t>
+    <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 8.1 og 8.2, og formlene for nullpunkt og risikomargin i formelsamlingen. Tallene er serviceavdelingen i Nordlys Elektro AS.</t>
   </si>
   <si>
     <t xml:space="preserve">Tre spaker, samme prosent, helt ulik virkning</t>
@@ -541,7 +541,7 @@
     <t xml:space="preserve">Prøv dette: sett prosenten i B4 til det nivået som gjør at tiltak C alene bringer avdelingen over nullpunktet. Se hvor stort kuttet må være.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Bok 1 kap. 8.3 om hvordan endringer i pris og kostnader flytter nullpunktet.</t>
+    <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 8.3 om hvordan endringer i pris og kostnader flytter nullpunktet.</t>
   </si>
   <si>
     <t xml:space="preserve">Hva en rabatt gjør med nullpunktet</t>
@@ -649,7 +649,7 @@
     <t xml:space="preserve">Prøv dette: skru rabatten i B5 oppover til dekningsbidraget i B12 blir null. Den prosenten er den absolutte grensen — og den ligger langt over det du bør godta.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Bok 1 kap. 8.3 og 8.4 om endret pris og om gjennomsnittspris når deler av volumet selges med rabatt.</t>
+    <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 8.3 og 8.4 om endret pris og om gjennomsnittspris når deler av volumet selges med rabatt.</t>
   </si>
   <si>
     <t xml:space="preserve">Skal serviceavdelingen legges ned?</t>
@@ -790,7 +790,7 @@
     <t xml:space="preserve">Legg merke til hva som skiller de to grensene i rad 20 og 21. Nullpunktet svarer på om avdelingen tjener penger. Nedleggelsesgrensen svarer på om Nordlys er tjent med å ha den. Det er to helt ulike spørsmål, og bare det ene står i læreboka.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Bok 1 kap. 8.1 til 8.4, og kapittel 2 om faste og variable kostnader. Skillet mellom unngåelige og ikke-unngåelige faste kostnader følger av bidragsmetoden i kapittel 5. Bransjetall: NHO Elektro, Lønnsomhetsrapport 2025, gjengitt i Elektro 24-7 19.08.2026 (hentet 10.09.2026). De 809 er bedriftene i datagrunnlaget, ikke bransjen. NHO Elektro oppgir ikke svarprosent.</t>
+    <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 8.1 til 8.4, og kapittel 2 om faste og variable kostnader. Skillet mellom unngåelige og ikke-unngåelige faste kostnader følger av bidragsmetoden i kapittel 5. Bransjetall: NHO Elektro, Lønnsomhetsrapport 2025, gjengitt i Elektro 24-7 19.08.2026 (hentet 10.09.2026). De 809 er bedriftene i datagrunnlaget, ikke bransjen. NHO Elektro oppgir ikke svarprosent.</t>
   </si>
   <si>
     <t xml:space="preserve">Din egen avdeling</t>
